--- a/data/site.xlsx
+++ b/data/site.xlsx
@@ -1479,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1558,1071 +1558,1054 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>pdf_url</t>
+          <t>site_name</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>assets/tiger-beetle-2026.pdf</t>
+          <t>虎甲自然</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>簡章下載路徑</t>
+          <t>網站名稱（logo 文字）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>site_name</t>
+          <t>nav_home</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>虎甲自然</t>
+          <t>企業概述</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>網站名稱（logo 文字）</t>
+          <t>導覽列：首頁</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>nav_home</t>
+          <t>nav_courses</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>企業概述</t>
+          <t>課程介紹</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>導覽列：首頁</t>
+          <t>導覽列：課程</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>nav_courses</t>
+          <t>nav_contact</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>課程介紹</t>
+          <t>聯絡我們</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>導覽列：課程</t>
+          <t>導覽列：聯絡</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>nav_contact</t>
+          <t>nav_download</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>聯絡我們</t>
+          <t>檔案下載</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>導覽列：聯絡</t>
+          <t>導覽列：下載</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>nav_download</t>
+          <t>nav_line</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>檔案下載</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>導覽列：下載</t>
+          <t>導覽列：右上 LINE 按鈕</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>nav_line</t>
+          <t>footer_pdf_label</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE</t>
+          <t>下載 PDF 簡章</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>導覽列：右上 LINE 按鈕</t>
+          <t>頁尾：PDF 連結文字</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>footer_pdf_label</t>
+          <t>footer_line_label</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>下載 PDF 簡章</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>頁尾：PDF 連結文字</t>
+          <t>頁尾：LINE 連結文字（會接上 line_oa_id）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>footer_line_label</t>
+          <t>footer_copyright</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE</t>
+          <t>© 虎甲自然 Tiger Beetle Nature · 城市與自然的引路者</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>頁尾：LINE 連結文字（會接上 line_oa_id）</t>
+          <t>頁尾版權文字</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>footer_copyright</t>
+          <t>home_hero_title</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>© 虎甲自然 Tiger Beetle Nature · 城市與自然的引路者</t>
+          <t>城市與自然的
+引路者</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>頁尾版權文字</t>
+          <t>首頁主標（\n=換行）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>home_hero_title</t>
+          <t>home_hero_subtitle</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>城市與自然的
-引路者</t>
+          <t>陪孩子走進步道，
+成為大自然的學生</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>首頁主標（\n=換行）</t>
+          <t>首頁副標（\n=換行）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>home_hero_subtitle</t>
+          <t>home_hero_courses_btn</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>陪孩子走進步道，
-成為大自然的學生</t>
+          <t>看課程介紹</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>首頁副標（\n=換行）</t>
+          <t>首頁 hero 按鈕：課程</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>home_hero_courses_btn</t>
+          <t>home_hero_line_btn</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>看課程介紹</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>首頁 hero 按鈕：課程</t>
+          <t>首頁 hero 按鈕：LINE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>home_hero_line_btn</t>
+          <t>register_url</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE</t>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdYiOmhPcmSpGkzhIr9cGwcwpl1vM6H52QdZGP3AW_nj55A8Q/viewform</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>首頁 hero 按鈕：LINE</t>
+          <t>線上報名 Google Form 連結</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>register_url</t>
+          <t>home_hero_register_btn</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/e/1FAIpQLSdYiOmhPcmSpGkzhIr9cGwcwpl1vM6H52QdZGP3AW_nj55A8Q/viewform</t>
+          <t>立即報名</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>線上報名 Google Form 連結</t>
+          <t>首頁 hero 按鈕：報名</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>home_hero_register_btn</t>
+          <t>home_about_heading</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>立即報名</t>
+          <t>關於虎甲自然</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>首頁 hero 按鈕：報名</t>
+          <t>首頁：品牌故事標題</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>home_about_heading</t>
+          <t>home_about_subtitle</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>關於虎甲自然</t>
+          <t>城市與自然之間，需要一位引路者</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>首頁：品牌故事標題</t>
+          <t>首頁：品牌故事副標</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>home_about_subtitle</t>
+          <t>home_about_more</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>城市與自然之間，需要一位引路者</t>
+          <t>閱讀完整故事</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>首頁：品牌故事副標</t>
+          <t>首頁：展開故事按鈕</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>home_about_more</t>
+          <t>home_series_heading</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>閱讀完整故事</t>
+          <t>三大課程系列</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>首頁：展開故事按鈕</t>
+          <t>首頁：系列區標題</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>home_series_heading</t>
+          <t>home_series_subtitle</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>三大課程系列</t>
+          <t>選擇適合孩子的節奏</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>首頁：系列區標題</t>
+          <t>首頁：系列區副標</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>home_series_subtitle</t>
+          <t>home_series_cta</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>選擇適合孩子的節奏</t>
+          <t>看班級 →</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>首頁：系列區副標</t>
+          <t>首頁：系列卡片按鈕</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>home_series_cta</t>
+          <t>home_keywords_heading</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>看班級 →</t>
+          <t>我們重視什麼</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>首頁：系列卡片按鈕</t>
+          <t>首頁：關鍵字區標題</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>home_keywords_heading</t>
+          <t>home_keywords_subtitle</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>我們重視什麼</t>
+          <t>點擊看更多</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>首頁：關鍵字區標題</t>
+          <t>首頁：關鍵字區副標</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>home_keywords_subtitle</t>
+          <t>home_cta_heading</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>點擊看更多</t>
+          <t>想了解更多？</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>首頁：關鍵字區副標</t>
+          <t>首頁：底部 CTA 標題</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>home_cta_heading</t>
+          <t>home_cta_text</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>想了解更多？</t>
+          <t>查看常見問題，或下載完整簡章認識虎甲自然。</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>首頁：底部 CTA 標題</t>
+          <t>首頁：底部 CTA 說明</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>home_cta_text</t>
+          <t>home_cta_faq_btn</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>查看常見問題，或下載完整簡章認識虎甲自然。</t>
+          <t>相關問題</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>首頁：底部 CTA 說明</t>
+          <t>首頁：底部 CTA 按鈕（FAQ）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>home_cta_faq_btn</t>
+          <t>home_cta_download_btn</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>相關問題</t>
+          <t>下載簡章</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>首頁：底部 CTA 按鈕（FAQ）</t>
+          <t>首頁：底部 CTA 按鈕（下載）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>home_cta_download_btn</t>
+          <t>home_register_heading</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>下載簡章</t>
+          <t>準備好走進山林了嗎？</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>首頁：底部 CTA 按鈕（下載）</t>
+          <t>首頁：報名區標題</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>home_register_heading</t>
+          <t>home_register_text</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>準備好走進山林了嗎？</t>
+          <t>填寫線上表單，我們會在 3 個工作天內回覆確認。</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>首頁：報名區標題</t>
+          <t>首頁：報名區說明</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>home_register_text</t>
+          <t>home_register_btn</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>填寫線上表單，我們會在 3 個工作天內回覆確認。</t>
+          <t>立即報名</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>首頁：報名區說明</t>
+          <t>首頁：報名區按鈕</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>home_register_btn</t>
+          <t>courses_hero_title</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>立即報名</t>
+          <t>課程介紹</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>首頁：報名區按鈕</t>
+          <t>課程頁：主標</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>courses_hero_title</t>
+          <t>courses_hero_subtitle</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>課程介紹</t>
+          <t>點班級卡片看完整課程細節</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>課程頁：主標</t>
+          <t>課程頁：副標</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>courses_hero_subtitle</t>
+          <t>courses_calendar_heading</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>點班級卡片看完整課程細節</t>
+          <t>課程行事曆</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>課程頁：副標</t>
+          <t>課程頁：行事曆標題</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>courses_calendar_heading</t>
+          <t>courses_calendar_subtitle</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>課程行事曆</t>
+          <t>依月份折疊，點開看當月各班級日期</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>課程頁：行事曆標題</t>
+          <t>課程頁：行事曆副標</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>courses_calendar_subtitle</t>
+          <t>courses_cta_heading</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>依月份折疊，點開看當月各班級日期</t>
+          <t>想多了解某個班級？</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>課程頁：行事曆副標</t>
+          <t>課程頁：底部 CTA 標題</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>courses_cta_heading</t>
+          <t>courses_cta_text</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>想多了解某個班級？</t>
+          <t>回到 LINE 一對一諮詢，或下載完整簡章。</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>課程頁：底部 CTA 標題</t>
+          <t>課程頁：底部 CTA 說明</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>courses_cta_text</t>
+          <t>courses_cta_line_btn</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE 一對一諮詢，或下載完整簡章。</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>課程頁：底部 CTA 說明</t>
+          <t>課程頁：底部 CTA 按鈕（LINE）</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>courses_cta_line_btn</t>
+          <t>courses_cta_download_btn</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE</t>
+          <t>下載簡章</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>課程頁：底部 CTA 按鈕（LINE）</t>
+          <t>課程頁：底部 CTA 按鈕（下載）</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>courses_cta_download_btn</t>
+          <t>class_card_more</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>下載簡章</t>
+          <t>看詳情</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>課程頁：底部 CTA 按鈕（下載）</t>
+          <t>課程卡片：看詳情按鈕</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>class_card_more</t>
+          <t>class_modal_fee_summary</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>看詳情</t>
+          <t>費用包含項目</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>課程卡片：看詳情按鈕</t>
+          <t>課程詳情：費用包含 摺疊標題</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>class_modal_fee_summary</t>
+          <t>class_modal_register_btn</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>費用包含項目</t>
+          <t>報名此班</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>課程詳情：費用包含 摺疊標題</t>
+          <t>課程詳情 Modal：報名按鈕</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>class_modal_register_btn</t>
+          <t>class_dates_empty</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>報名此班</t>
+          <t>尚未公布日期</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>課程詳情 Modal：報名按鈕</t>
+          <t>課程詳情：無日期時顯示</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>class_dates_empty</t>
+          <t>class_list_empty</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>尚未公布日期</t>
+          <t>本系列暫無班級</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>課程詳情：無日期時顯示</t>
+          <t>課程頁：系列無班級時顯示</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>class_list_empty</t>
+          <t>calendar_empty</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>本系列暫無班級</t>
+          <t>尚未公布行事曆</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>課程頁：系列無班級時顯示</t>
+          <t>課程頁：行事曆無資料時顯示</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>calendar_empty</t>
+          <t>info_hero_title</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>尚未公布行事曆</t>
+          <t>相關問題</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>課程頁：行事曆無資料時顯示</t>
+          <t>問題頁：主標</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>info_hero_title</t>
+          <t>info_hero_subtitle</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>相關問題</t>
+          <t>常見問題、退費規定、個資聲明、聯絡與簡章下載</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>問題頁：主標</t>
+          <t>問題頁：副標</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>info_hero_subtitle</t>
+          <t>info_faq_heading</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>常見問題、退費規定、個資聲明、聯絡與簡章下載</t>
+          <t>常見問題</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>問題頁：副標</t>
+          <t>問題頁：FAQ 標題</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>info_faq_heading</t>
+          <t>info_refund_heading</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>常見問題</t>
+          <t>退費規定</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>問題頁：FAQ 標題</t>
+          <t>問題頁：退費標題</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>info_refund_heading</t>
+          <t>info_refund_intro</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>退費規定</t>
+          <t>本課程為系列課程，為保障師生權益與保險辦理，依開課日與退費階段不同有對應比例。</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費標題</t>
+          <t>問題頁：退費前言</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>info_refund_intro</t>
+          <t>info_refund_summary</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>本課程為系列課程，為保障師生權益與保險辦理，依開課日與退費階段不同有對應比例。</t>
+          <t>查看完整退費規定（4 階段）</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費前言</t>
+          <t>問題頁：退費摺疊標題</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>info_refund_summary</t>
+          <t>info_refund_note</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>查看完整退費規定（4 階段）</t>
+          <t>行政院公告天災或其他不可抗力因素取消，將另行協議補課日期。</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費摺疊標題</t>
+          <t>問題頁：退費補充說明</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>info_refund_note</t>
+          <t>info_refund_col_time</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>行政院公告天災或其他不可抗力因素取消，將另行協議補課日期。</t>
+          <t>退費時間</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費補充說明</t>
+          <t>問題頁：退費表欄一</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>info_refund_col_time</t>
+          <t>info_refund_col_ratio</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>退費時間</t>
+          <t>退費比例</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費表欄一</t>
+          <t>問題頁：退費表欄二</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>info_refund_col_ratio</t>
+          <t>info_privacy_heading</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>退費比例</t>
+          <t>個人資料保護聲明</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>問題頁：退費表欄二</t>
+          <t>問題頁：個資標題</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>info_privacy_heading</t>
+          <t>info_privacy_intro</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>個人資料保護聲明</t>
+          <t>我們蒐集的個資僅供課程聯繫、保險投保及緊急聯絡使用，絕不提供給第三方。</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>問題頁：個資標題</t>
+          <t>問題頁：個資前言</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>info_privacy_intro</t>
+          <t>info_privacy_summary</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>我們蒐集的個資僅供課程聯繫、保險投保及緊急聯絡使用，絕不提供給第三方。</t>
+          <t>查看完整聲明</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>問題頁：個資前言</t>
+          <t>問題頁：個資摺疊標題</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>info_privacy_summary</t>
+          <t>info_contact_heading</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>查看完整聲明</t>
+          <t>聯絡我們</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>問題頁：個資摺疊標題</t>
+          <t>問題頁：聯絡標題</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>info_contact_heading</t>
+          <t>info_contact_line_btn</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>聯絡我們</t>
+          <t>回到 LINE</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>問題頁：聯絡標題</t>
+          <t>問題頁：聯絡 LINE 按鈕</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>info_contact_line_btn</t>
+          <t>info_contact_email_btn</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>回到 LINE</t>
+          <t>來信詢問</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>問題頁：聯絡 LINE 按鈕</t>
+          <t>問題頁：聯絡 Email 按鈕</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>info_contact_email_btn</t>
+          <t>info_download_heading</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>來信詢問</t>
+          <t>檔案下載</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>問題頁：聯絡 Email 按鈕</t>
+          <t>問題頁：下載標題</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>info_download_heading</t>
+          <t>info_pdf_title</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>檔案下載</t>
+          <t>虎甲自然完整簡章 PDF</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>問題頁：下載標題</t>
+          <t>問題頁：PDF 卡片標題</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>info_pdf_title</t>
+          <t>info_pdf_hint</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>虎甲自然完整簡章 PDF</t>
+          <t>完整版本，可分享給其他家長</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>問題頁：PDF 卡片標題</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>info_pdf_hint</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>完整版本，可分享給其他家長</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>問題頁：PDF 卡片說明</t>
         </is>
